--- a/output/data_checks/missing_by_country_variable.xlsx
+++ b/output/data_checks/missing_by_country_variable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ems/projects/macro3_project/output/data_checks/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{4BF9BE45-BC3D-C44A-9FCC-157283D4C02A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{1BBCBC4E-3355-C047-9042-F8073F95A734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3480" yWindow="2700" windowWidth="27640" windowHeight="16680" xr2:uid="{B6CD0651-DF8C-F943-8C5B-2D4B9D3444DC}"/>
   </bookViews>
@@ -1794,7 +1794,7 @@
       <c r="C15" t="s">
         <v>12</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E15">
